--- a/Paket_2_Bahasa_Indonesia_TKA_SD.xlsx
+++ b/Paket_2_Bahasa_Indonesia_TKA_SD.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paket 2 Bahasa" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -471,27 +471,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Bahasa 1: contoh soal pemahaman teks.</t>
+          <t>Berdasarkan teks 'Energi Surya: Sumber Daya Tak Terbatas untuk Masa Depan', alat yang berfungsi mengubah foton sinar matahari menjadi energi listrik adalah....</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Kincir angin modern</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Panel surya (sel fotovoltaik)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Turbin generator uap</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Pipa transmisi bawah laut</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -502,7 +502,11 @@
       <c r="H2" t="n">
         <v>60</v>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -512,27 +516,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Bahasa 2: contoh soal pemahaman teks.</t>
+          <t>Mengapa Indonesia memiliki potensi pemanfaatan energi surya yang sangat besar?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Karena Indonesia memiliki banyak cadangan bahan bakar fosil batu bara</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Karena letak geografis Indonesia berada di garis khatulistiwa dengan sinar matahari sepanjang tahun</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Karena biaya pemasangan panel surya di Indonesia gratis dari pemerintah</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Karena pulau-pulau di Indonesia tidak memerlukan jaringan kabel listrik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -543,7 +547,11 @@
       <c r="H3" t="n">
         <v>60</v>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -553,27 +561,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Bahasa 3: contoh soal pemahaman teks.</t>
+          <t>Makna istilah 'energi terbarukan' pada paragraf pertama teks informasi di atas adalah....</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Energi yang berasal dari pengolahan minyak bumi dan gas alam</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Energi yang dapat diproduksi kembali secara terus-menerus dan tidak akan pernah habis</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Energi listrik bertegangan tinggi yang disalurkan melalui kabel udara</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Energi yang hanya dapat diperbarui setiap sepuluh tahun sekali</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -584,37 +592,41 @@
       <c r="H4" t="n">
         <v>60</v>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Bahasa 4: contoh soal pemahaman teks.</t>
+          <t>Manakah pernyataan berikut yang SESUAI dengan isi teks mengenai energi surya? (Pilihlah lebih dari satu jawaban benar!)  [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Energi surya menghasilkan emisi gas buang karbon yang mencemari udara.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  PLTS dapat menjadi solusi penyediaan listrik bagi pulau-pulau terpencil dan pelosok.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Pemanfaatan energi surya dapat mengurangi ketergantungan pada bahan bakar fosil.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Di Indonesia sinar matahari hanya muncul selama 4 jam setiap hari.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -625,7 +637,11 @@
       <c r="H5" t="n">
         <v>60</v>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -635,27 +651,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Bahasa 5: contoh soal pemahaman teks.</t>
+          <t>Ide pokok yang terdapat pada paragraf kedua teks informasi tersebut adalah....</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Besarnya potensi dan pemanfaatan energi surya di wilayah Indonesia</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Harga jual panel surya di kawasan perkotaan dan pedesaan</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Proses peleburan silikon pada pembuatan sel fotovoltaik</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Dampak buruk batu bara terhadap kerusakan atmosfer bumi</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -666,17 +682,21 @@
       <c r="H6" t="n">
         <v>60</v>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Bahasa 6: contoh soal pemahaman teks.</t>
+          <t>Tentukan kebenaran dari pernyataan berikut berdasarkan bacaan energi surya!  [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -707,7 +727,11 @@
       <c r="H7" t="n">
         <v>60</v>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -717,27 +741,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Bahasa 7: contoh soal pemahaman teks.</t>
+          <t>Simpulan yang paling tepat dari teks bacaan energi surya adalah.... Bacalah cerita fiksi berikut dengan cermat untuk menjawab soal nomor 8 sampai 14!
+Persahabatan Elang dan Merpati
+Di sebuah hutan yang lebat, hiduplah Gagah si burung Elang yang berbadan tegap dan sayap perkasa, serta Putih si burung Merpati yang lincah dan berbulu bersih. Gagah sering merasa bangga dengan kekuatannya mencengkeram mangsa dan terbang tinggi menembus badai. Sebaliknya, Putih selalu rendah hati dan gemar menolong binatang-binatang lain yang tersesat di dalam hutan.
+Suatu sore menjelang musim hujan, langit berubah menjadi gelap pekat disertai angin kencang. Gagah yang sedang terbang di ketinggian tiba-tiba tersambar angin puyuh yang sangat dahsyat. Sayap kanannya terhantam dahan pohon beringin yang patah hingga ia terjatuh ke semak-semak berduri, tak berdaya. Gagah merintih kesakitan dan tidak sanggup mengepakkan sayapnya lagi.
+Melihat keadaan Gagah, Putih tidak tinggal diam. Ia segera terbang memanggil kawan-kawan binatang di hutan untuk membawakan dedaunan obat. Dengan telaten, Putih merawat luka pada sayap Gagah dan membawakannya biji-bijian serta air minum setiap hari. Setelah beberapa pekan, sayap Gagah pun sembuh. Gagah menundukkan kepalanya dengan rasa malu bercampur haru, "Maafkan kesombonganku selama ini, Putih. Tanpa pertolonganmu yang tulus, aku mungkin sudah mati di semak-semak itu." Sejak saat itu, Gagah menjadi pelindung yang setia bagi Putih dan seluruh penghuni hutan.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Indonesia harus segera menutup seluruh pertambangan batu bara bulan depan.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Energi surya adalah alternatif energi bersih yang potensial di Indonesia untuk menggantikan energi fosil.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Panel surya hanya efektif dipasang di perumahan kota besar.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Kabel transmisi listrik konvensional sudah tidak diperlukan lagi di masa depan.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -748,7 +776,11 @@
       <c r="H8" t="n">
         <v>60</v>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -758,27 +790,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Bahasa 8: contoh soal pemahaman teks.</t>
+          <t>Watak tokoh Putih dalam fabel 'Persahabatan Elang dan Merpati' adalah....</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Pengecut dan tidak peduli</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Rendah hati, penolong, dan tulus</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Pemalas dan suka bergantung pada orang lain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Pendendam dan suka pamer kebaikan</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -789,7 +821,11 @@
       <c r="H9" t="n">
         <v>60</v>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -799,27 +835,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Bahasa 9: contoh soal pemahaman teks.</t>
+          <t>Peristiwa awal yang menjadi penyebab terjadinya konflik (masalah) dalam cerita fiksi di atas adalah....</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Putih menolak terbang bersama Gagah di atas hutan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Gagah tersambar angin puyuh hingga sayapnya patah terhantam dahan beringin</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Seluruh binatang di hutan mengusir Gagah karena kesombongannya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Hutan tempat tinggal mereka terbakar oleh sambaran petir</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -830,7 +866,11 @@
       <c r="H10" t="n">
         <v>60</v>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -840,27 +880,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Bahasa 10: contoh soal pemahaman teks.</t>
+          <t>Makna ungkapan 'rendah hati' yang dimiliki tokoh Putih dalam cerita adalah....</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Merasa dirinya serba kekurangan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Tidak sombong atau tidak angkuh</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Berbadan kecil dan lemah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Mudah merasa sedih dan kecewa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -871,37 +911,41 @@
       <c r="H11" t="n">
         <v>60</v>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Bahasa 11: contoh soal pemahaman teks.</t>
+          <t>Perubahan sikap apa yang dialami tokoh Gagah setelah sembuh dari lukanya?  [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Menyadari kesalahannya dan meminta maaf atas kesombongan masa lalunya.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Menjadi burung yang setia melindungi Putih dan penghuni hutan lainnya.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Memutuskan pergi meninggalkan hutan untuk mencari kawan baru.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Kembali membanggakan kekuatannya di hadapan burung-burung kecil.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -912,7 +956,11 @@
       <c r="H12" t="n">
         <v>60</v>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -922,27 +970,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Bahasa 12: contoh soal pemahaman teks.</t>
+          <t>Pesan moral atau amanat yang dapat dipetik dari fabel tersebut adalah....</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Kekuatan fisik adalah segalanya dalam menentukan persahabatan sejati.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Jangan pernah bersikap sombong karena setiap makhluk pasti membutuhkan pertolongan orang lain suatu saat.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Jangan terbang saat langit gelap karena berbahaya tersambar petir.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Tolonglah teman hanya jika teman tersebut memiliki kekuatan besar.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -953,17 +1001,21 @@
       <c r="H13" t="n">
         <v>60</v>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Bahasa 13: contoh soal pemahaman teks.</t>
+          <t>Tentukan kesesuaian dari pernyataan berikut terkait perilaku tokoh fabel dengan kehidupan sehari-hari!  [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -994,7 +1046,11 @@
       <c r="H14" t="n">
         <v>60</v>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1004,27 +1060,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Bahasa 14: contoh soal pemahaman teks.</t>
+          <t>Ungkapan yang tepat untuk menggambarkan sifat Gagah SEBELUM ia tertimpa musibah angin puyuh adalah....</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Panjang tangan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Besar kepala</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Ringan tangan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Keras kepala</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1035,7 +1091,11 @@
       <c r="H15" t="n">
         <v>60</v>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1045,27 +1105,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Bahasa 15: contoh soal pemahaman teks.</t>
+          <t>Penulisan tanda baca yang tepat untuk perincian barang dalam kalimat berikut adalah....</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Ibu membeli perlengkapan dapur: wajan panci, pisau dan sutil.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Ibu membeli perlengkapan dapur; wajan, panci, pisau, dan sutil.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Ibu membeli perlengkapan dapur: wajan, panci, pisau, dan sutil.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Ibu membeli perlengkapan dapur, wajan: panci: pisau: dan sutil.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1076,7 +1136,11 @@
       <c r="H16" t="n">
         <v>60</v>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1086,27 +1150,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Bahasa 16: contoh soal pemahaman teks.</t>
+          <t>Perhatikan kalimat rumpang berikut:
+Para relawan sedang [...] paket sembako untuk korban bencana banjir.
+Kata berimbuhan yang paling tepat untuk melengkapi kalimat tersebut adalah....</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  membagi-bagikan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  dibagi-bagikan</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  kebagian</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  berbagikan</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1117,7 +1183,11 @@
       <c r="H17" t="n">
         <v>60</v>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1127,27 +1197,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Bahasa 17: contoh soal pemahaman teks.</t>
+          <t>Kelompok kata berikut yang SELURUHNYA merupakan kata baku adalah....</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Izin, nasihat, kualitas, sistem</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Ijin, nasehat, kwalitas, sistim</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Izin, nasehat, kualitas, sistim</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Ijin, nasihat, kwalitas, sistem</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1158,37 +1228,43 @@
       <c r="H18" t="n">
         <v>60</v>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Bahasa 18: contoh soal pemahaman teks.</t>
+          <t>Perhatikan kalimat tidak efektif berikut:
+"Bagi para peserta lomba yang mana belum mendaftar ulang harap segera mendaftar."
+Manakah perbaikan kalimat di atas agar menjadi KALIMAT EFEKTIF?  [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Peserta lomba yang belum mendaftar ulang harap segera mendaftar.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Para peserta lomba yang belum mendaftar ulang harap segera mendaftar.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Bagi para peserta-peserta yang mana belum mendaftar ulang harap daftar.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Semua peserta lomba yang mana belum mendaftar ulang diharapkan segera daftar.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1199,7 +1275,11 @@
       <c r="H19" t="n">
         <v>60</v>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1209,27 +1289,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Bahasa 19: contoh soal pemahaman teks.</t>
+          <t>Perhatikan kalimat-kalimat hasil pengamatan berikut:
+(1) Bunga mawar tersebut mulai mekar dan mengeluarkan aroma wangi.
+(2) Siswa kelas 6 mengamati pertumbuhan tanaman mawar di kebun sekolah.
+(3) Batang tanaman mawar dipenuhi duri tajam dan daun berwarna hijau segar.
+(4) Pengamatan dilakukan setiap pagi hari selama dua minggu berturut-turut.
+Urutan kalimat yang padu untuk membentuk teks laporan hasil pengamatan adalah....</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  (2) - (4) - (3) - (1)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  (2) - (3) - (4) - (1)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  (4) - (2) - (1) - (3)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  (3) - (1) - (2) - (4)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1240,17 +1325,21 @@
       <c r="H20" t="n">
         <v>60</v>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Bahasa 20: contoh soal pemahaman teks.</t>
+          <t>Tentukan kesesuaian penulisan judul karangan berikut menurut kaidah Ejaan Bahasa Indonesia (EBI)!  [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1281,7 +1370,11 @@
       <c r="H21" t="n">
         <v>60</v>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
